--- a/output/pdf_financials_xlsx/GIII.xlsx
+++ b/output/pdf_financials_xlsx/GIII.xlsx
@@ -1321,40 +1321,40 @@
         <v>34.07907</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.456489</v>
+        <v>-2.456489</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.373444</v>
+        <v>-3.373444</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.152975</v>
+        <v>-2.152975</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>5.322531</v>
+        <v>-5.322531</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>7.70768</v>
+        <v>-7.70768</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.742369</v>
+        <v>-4.742369</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.727813</v>
+        <v>-4.727813</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>24.935756</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>11.462071</v>
+        <v>0.161501</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>7.524133</v>
+        <v>0.050155</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>7.792422</v>
+        <v>0.137072</v>
       </c>
     </row>
     <row r="17">
@@ -1376,10 +1376,10 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-9.764099999999999</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-17.682004</v>
+        <v>-50.476136</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1631,46 +1631,46 @@
         <v>-22.07867</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.88205</v>
+        <v>-4.88205</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16.397066</v>
+        <v>-16.397066</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.456489</v>
+        <v>-2.456489</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.373444</v>
+        <v>-3.373444</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.152975</v>
+        <v>-2.152975</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>5.322531</v>
+        <v>-5.322531</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>7.70768</v>
+        <v>-7.70768</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>4.742369</v>
+        <v>-4.742369</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>4.727813</v>
+        <v>-4.727813</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>12.467878</v>
+        <v>-12.467878</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>5.650285</v>
+        <v>-5.650285</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>3.736989</v>
+        <v>-3.736989</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3.827675</v>
+        <v>-3.827675</v>
       </c>
     </row>
     <row r="21">
@@ -1814,46 +1814,46 @@
         <v>-22.07867</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.88205</v>
+        <v>-4.88205</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16.397066</v>
+        <v>-16.397066</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.456489</v>
+        <v>-2.456489</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.373444</v>
+        <v>-3.373444</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.152975</v>
+        <v>-2.152975</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.322531</v>
+        <v>-5.322531</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.70768</v>
+        <v>-7.70768</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.742369</v>
+        <v>-4.742369</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>4.727813</v>
+        <v>-4.727813</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.467878</v>
+        <v>-12.467878</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.650285</v>
+        <v>-5.650285</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>3.736989</v>
+        <v>-3.736989</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3.827675</v>
+        <v>-3.827675</v>
       </c>
     </row>
     <row r="24">
@@ -2005,46 +2005,46 @@
         <v>95.99421700000001</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>122.05125</v>
+        <v>-122.05125</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>126.131277</v>
+        <v>-126.131277</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>122.82445</v>
+        <v>-122.82445</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>25.949569</v>
+        <v>-25.949569</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>26.912188</v>
+        <v>-26.912188</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>48.386645</v>
+        <v>-48.386645</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>64.230667</v>
+        <v>-64.230667</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>74.563438</v>
+        <v>-74.563438</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>79.039483</v>
+        <v>-79.039483</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>118.195325</v>
+        <v>-118.195325</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>113.344345</v>
+        <v>-113.344345</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>113.0057</v>
+        <v>-113.0057</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>124.5663</v>
+        <v>-124.5663</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>127.589167</v>
+        <v>-127.589167</v>
       </c>
     </row>
     <row r="27">
@@ -2072,40 +2072,40 @@
         <v>34.07907</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.456489</v>
+        <v>-2.456489</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.373444</v>
+        <v>-3.373444</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.152975</v>
+        <v>-2.152975</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5.322531</v>
+        <v>-5.322531</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>7.70768</v>
+        <v>-7.70768</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>4.742369</v>
+        <v>-4.742369</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.727813</v>
+        <v>-4.727813</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>24.935756</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>11.462071</v>
+        <v>0.161501</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>7.524133</v>
+        <v>0.050155</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>7.792422</v>
+        <v>0.137072</v>
       </c>
     </row>
     <row r="28">
@@ -2194,40 +2194,40 @@
         <v>34.07907</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.456489</v>
+        <v>-2.456489</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.373444</v>
+        <v>-3.373444</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.152975</v>
+        <v>-2.152975</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.322531</v>
+        <v>-5.322531</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>7.70768</v>
+        <v>-7.70768</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>4.742369</v>
+        <v>-4.742369</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.727813</v>
+        <v>-4.727813</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>24.935756</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>11.462071</v>
+        <v>0.161501</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.524133</v>
+        <v>0.050155</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>7.792422</v>
+        <v>0.137072</v>
       </c>
     </row>
     <row r="30">
@@ -2346,46 +2346,48 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>51.8852304361592</v>
+        <v>148.1147695638408</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>50</v>
+        <v>-0</v>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>50.70450183042837</v>
+        <v>3598.606819772014</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>50.33329421476201</v>
+        <v>7550.880271159405</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>50.87952115529677</v>
+        <v>2892.45578965799</v>
       </c>
     </row>
     <row r="32">
@@ -6572,16 +6574,16 @@
         <v>-4.727813</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>12.467878</v>
+        <v>-12.467878</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>5.650285</v>
+        <v>-5.650285</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>3.736989</v>
+        <v>-3.736989</v>
       </c>
       <c r="S99" s="3" t="n">
-        <v>3.827675</v>
+        <v>-3.827675</v>
       </c>
     </row>
     <row r="100">
@@ -44870,46 +44872,46 @@
         </is>
       </c>
       <c r="I349" s="5" t="n">
-        <v>4.88205</v>
+        <v>-4.88205</v>
       </c>
       <c r="J349" s="5" t="n">
-        <v>16.397066</v>
+        <v>-16.397066</v>
       </c>
       <c r="K349" s="5" t="n">
-        <v>2.456489</v>
+        <v>-2.456489</v>
       </c>
       <c r="L349" s="5" t="n">
-        <v>3.373444</v>
+        <v>-3.373444</v>
       </c>
       <c r="M349" s="5" t="n">
-        <v>2.152975</v>
+        <v>-2.152975</v>
       </c>
       <c r="N349" s="5" t="n">
-        <v>5.322531</v>
+        <v>-5.322531</v>
       </c>
       <c r="O349" s="5" t="n">
-        <v>7.70768</v>
+        <v>-7.70768</v>
       </c>
       <c r="P349" s="5" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="Q349" s="5" t="n">
-        <v>4.742369</v>
+        <v>-4.742369</v>
       </c>
       <c r="R349" s="5" t="n">
-        <v>4.727813</v>
+        <v>-4.727813</v>
       </c>
       <c r="S349" s="5" t="n">
-        <v>12.467878</v>
+        <v>-12.467878</v>
       </c>
       <c r="T349" s="5" t="n">
-        <v>5.650285</v>
+        <v>-5.650285</v>
       </c>
       <c r="U349" s="5" t="n">
-        <v>3.736989</v>
+        <v>-3.736989</v>
       </c>
       <c r="V349" s="5" t="n">
-        <v>3.827675</v>
+        <v>-3.827675</v>
       </c>
     </row>
     <row r="350">
@@ -45117,13 +45119,13 @@
         </is>
       </c>
       <c r="T351" s="5" t="n">
-        <v>5.646457</v>
+        <v>-5.646457</v>
       </c>
       <c r="U351" s="5" t="n">
-        <v>3.729334</v>
+        <v>-3.729334</v>
       </c>
       <c r="V351" s="5" t="n">
-        <v>3.839158</v>
+        <v>-3.839158</v>
       </c>
     </row>
     <row r="352">
@@ -50456,13 +50458,13 @@
         </is>
       </c>
       <c r="O402" s="5" t="n">
-        <v>7.738301</v>
+        <v>-7.738301</v>
       </c>
       <c r="P402" s="5" t="n">
-        <v>5.965075</v>
+        <v>-5.965075</v>
       </c>
       <c r="Q402" s="5" t="n">
-        <v>4.719404</v>
+        <v>-4.719404</v>
       </c>
       <c r="R402" t="inlineStr">
         <is>
@@ -50470,10 +50472,10 @@
         </is>
       </c>
       <c r="S402" s="5" t="n">
-        <v>12.471706</v>
+        <v>-12.471706</v>
       </c>
       <c r="T402" s="5" t="n">
-        <v>5.646457</v>
+        <v>-5.646457</v>
       </c>
       <c r="U402" t="inlineStr">
         <is>
@@ -51597,10 +51599,10 @@
         </is>
       </c>
       <c r="N413" s="5" t="n">
-        <v>4.943353</v>
+        <v>-4.943353</v>
       </c>
       <c r="O413" s="5" t="n">
-        <v>7.738301</v>
+        <v>-7.738301</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -51608,10 +51610,10 @@
         </is>
       </c>
       <c r="Q413" s="5" t="n">
-        <v>4.719404</v>
+        <v>-4.719404</v>
       </c>
       <c r="R413" s="5" t="n">
-        <v>4.735468</v>
+        <v>-4.735468</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
@@ -58626,10 +58628,10 @@
         </is>
       </c>
       <c r="M480" s="5" t="n">
-        <v>2.154543</v>
+        <v>-2.154543</v>
       </c>
       <c r="N480" s="5" t="n">
-        <v>4.943353</v>
+        <v>-4.943353</v>
       </c>
       <c r="O480" t="inlineStr">
         <is>
@@ -60392,13 +60394,13 @@
         </is>
       </c>
       <c r="K497" s="5" t="n">
-        <v>2.580793</v>
+        <v>-2.580793</v>
       </c>
       <c r="L497" s="5" t="n">
-        <v>3.357632</v>
+        <v>-3.357632</v>
       </c>
       <c r="M497" s="5" t="n">
-        <v>2.154543</v>
+        <v>-2.154543</v>
       </c>
       <c r="N497" t="inlineStr">
         <is>
@@ -61844,13 +61846,13 @@
         </is>
       </c>
       <c r="I511" s="5" t="n">
-        <v>0.400818</v>
+        <v>-0.400818</v>
       </c>
       <c r="J511" s="5" t="n">
-        <v>1.282764</v>
+        <v>-1.282764</v>
       </c>
       <c r="K511" s="5" t="n">
-        <v>0.124304</v>
+        <v>-0.124304</v>
       </c>
       <c r="L511" t="inlineStr">
         <is>
@@ -61950,13 +61952,13 @@
         </is>
       </c>
       <c r="I512" s="5" t="n">
-        <v>5.282868</v>
+        <v>-5.282868</v>
       </c>
       <c r="J512" s="5" t="n">
-        <v>17.67983</v>
+        <v>-17.67983</v>
       </c>
       <c r="K512" s="5" t="n">
-        <v>2.580793</v>
+        <v>-2.580793</v>
       </c>
       <c r="L512" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GIII.xlsx
+++ b/output/pdf_financials_xlsx/GIII.xlsx
@@ -1068,49 +1068,49 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02803</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.315195</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.091392</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06331199999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.192503</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.175306</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.049494</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.071241</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026889</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003277</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.042476</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.052927</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06576</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.03537</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008695</v>
       </c>
     </row>
     <row r="13">
@@ -2063,49 +2063,49 @@
         <v>-0.094458</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-22.07867</v>
+        <v>-22.1067</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.88205</v>
+        <v>5.197245</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>34.07907</v>
+        <v>34.170462</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.456489</v>
+        <v>-2.393177</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.373444</v>
+        <v>-3.180941</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.152975</v>
+        <v>-1.977669</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.322531</v>
+        <v>-5.273037</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.70768</v>
+        <v>-7.636439</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.965075</v>
+        <v>-5.938186</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.742369</v>
+        <v>-4.739092</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.727813</v>
+        <v>-4.685337</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
+        <v>0.052927</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.161501</v>
+        <v>0.227261</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.050155</v>
+        <v>0.085525</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.137072</v>
+        <v>0.145767</v>
       </c>
     </row>
     <row r="28">
@@ -2185,49 +2185,49 @@
         <v>-0.094458</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-22.07867</v>
+        <v>-22.1067</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.88205</v>
+        <v>5.197245</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.07907</v>
+        <v>34.170462</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.456489</v>
+        <v>-2.393177</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.373444</v>
+        <v>-3.180941</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.152975</v>
+        <v>-1.977669</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.322531</v>
+        <v>-5.273037</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.70768</v>
+        <v>-7.636439</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.965075</v>
+        <v>-5.938186</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.742369</v>
+        <v>-4.739092</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.727813</v>
+        <v>-4.685337</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>0.052927</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.161501</v>
+        <v>0.227261</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.050155</v>
+        <v>0.085525</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.137072</v>
+        <v>0.145767</v>
       </c>
     </row>
     <row r="30">
@@ -2501,16 +2501,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.449101</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00495</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.6523949999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>27.23027</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>13.279022</v>
@@ -2543,16 +2543,16 @@
         <v>7.734986</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.718398</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.149346</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.280212</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.04475</v>
       </c>
     </row>
     <row r="35">
@@ -2623,16 +2623,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.449101</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00495</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.6523949999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>27.23027</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>13.279022</v>
@@ -2665,16 +2665,16 @@
         <v>7.734986</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.718398</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.149346</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.280212</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.04475</v>
       </c>
     </row>
     <row r="37">
@@ -3355,16 +3355,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.466359</v>
+        <v>0.017258</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.355358</v>
+        <v>0.350408</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>27.397853</v>
+        <v>0.167583</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.248239</v>
@@ -3397,16 +3397,16 @@
         <v>0.258118</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.862926</v>
+        <v>0.144528</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.399272</v>
+        <v>0.249926</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.498262</v>
+        <v>0.21805</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.180488</v>
+        <v>0.135738</v>
       </c>
     </row>
     <row r="49">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -43254,7 +43254,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -55132,7 +55132,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -57638,7 +57638,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -63300,7 +63300,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">

--- a/output/pdf_financials_xlsx/GIII.xlsx
+++ b/output/pdf_financials_xlsx/GIII.xlsx
@@ -7334,13 +7334,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.060514</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.088445</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.007662</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.076478</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -33440,7 +33440,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GIII.xlsx
+++ b/output/pdf_financials_xlsx/GIII.xlsx
@@ -1309,7 +1309,7 @@
         <v>-0.075236</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.094458</v>
+        <v>-0.181174</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-22.07867</v>
@@ -1370,10 +1370,10 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.086716</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.082291</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-9.764099999999999</v>
@@ -2060,7 +2060,7 @@
         <v>-0.075236</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.094458</v>
+        <v>-0.181174</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-22.1067</v>
@@ -2182,7 +2182,7 @@
         <v>-0.075236</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.094458</v>
+        <v>-0.181174</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-22.1067</v>
@@ -2340,10 +2340,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-47.86337995518121</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3727171971862436</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>200</v>
@@ -36928,7 +36928,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -37246,7 +37250,11 @@
           <t>Shares issued for cash (note 10b)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -38202,7 +38210,11 @@
           <t>Deferred income tax expense 4,425</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -38934,7 +38946,11 @@
           <t>Shares issued for cash (note 10) 39,103,892</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -41696,7 +41712,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E317" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -44746,7 +44766,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -48084,7 +48108,11 @@
           <t>Deferred income tax recovery (note 16)</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -62770,7 +62798,11 @@
           <t>Income tax (recovery) expense (note 16)</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -64148,7 +64180,11 @@
           <t>Income tax recovery (expense) (note 16)</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -66154,7 +66190,11 @@
           <t>Current income tax recovery (expense) 4,425</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -66362,7 +66402,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
